--- a/Mock_Test_Bilingual_Question_Bank_Template.xlsx
+++ b/Mock_Test_Bilingual_Question_Bank_Template.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -488,95 +488,100 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Cognitive Level</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Local Passage No.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Question Order</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Question English</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Question Assamese</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Option A English</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Option A Assamese</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Option B English</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Option B Assamese</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Option C English</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Option C Assamese</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Option D English</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Option D Assamese</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
@@ -620,85 +625,87 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>What is a plant?</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>উদ্ভিদ কি?</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>গছ</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Animal</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>প্ৰাণী</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Rock</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>শিল</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Water</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>পানী</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -738,87 +745,90 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Understanding</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>English passage question 1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>অসমীয়া passage প্ৰশ্ন 1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>ক</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>খ</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>গ</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>ঘ</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -858,87 +868,90 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Understanding</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>English passage question 2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>অসমীয়া passage প্ৰশ্ন 2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>ক</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>খ</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>গ</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>ঘ</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -978,87 +991,90 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Understanding</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>English passage question 3</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>অসমীয়া passage প্ৰশ্ন 3</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>ক</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>খ</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>গ</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>ঘ</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1098,87 +1114,90 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Understanding</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>English passage question 4</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>অসমীয়া passage প্ৰশ্ন 4</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>ক</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>খ</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>গ</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>ঘ</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1218,87 +1237,90 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Understanding</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>P-001</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>English passage question 5</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>অসমীয়া passage প্ৰশ্ন 5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>ক</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>খ</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>গ</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>ঘ</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1326,7 +1348,6 @@
           <t>Number System</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>NO</t>
@@ -1334,85 +1355,87 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Application</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Find the value of 2+2</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2+2 ৰ মান উলিওৱা</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>৩</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>৪</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>৫</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>৬</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Z8"/>
@@ -1426,7 +1449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,6 +1498,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>MAT remains COMMON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Common: write YES for questions frequently asked in exams (any Difficulty level); NO or blank otherwise. Questions in the same Variation Group as a Common question are treated as Common automatically.</t>
         </is>
       </c>
     </row>
